--- a/data/trans_dic/IP31KM16_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,04; 52,79</t>
+          <t>8,47; 26,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 26,67</t>
+          <t>14,9; 35,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,98; 36,87</t>
+          <t>13,82; 27,16</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 14,85</t>
+          <t>9,27; 18,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 20,5</t>
+          <t>9,93; 15,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,69</t>
+          <t>10,44; 15,93</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 17,54</t>
+          <t>7,67; 17,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 16,98</t>
+          <t>7,7; 16,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 15,08</t>
+          <t>8,82; 15,49</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 16,59</t>
+          <t>10,31; 16,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 17,57</t>
+          <t>10,84; 15,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 15,28</t>
+          <t>11,12; 15,0</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>19766</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9149; 28350</t>
+          <t>4551; 14057</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5161; 15559</t>
+          <t>6838; 16474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16787; 41306</t>
+          <t>13772; 27054</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>53514</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>62812</t>
+          <t>52604</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116326</t>
+          <t>111173</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41184; 67088</t>
+          <t>43232; 84900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47640; 103583</t>
+          <t>42171; 64289</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95854; 150150</t>
+          <t>93037; 141978</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>37270</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10887; 25643</t>
+          <t>12781; 29037</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14041; 30754</t>
+          <t>11331; 24997</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28914; 49370</t>
+          <t>27685; 48607</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>87588</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168209</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69781; 108149</t>
+          <t>70780; 112471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76109; 130845</t>
+          <t>66982; 95205</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154224; 213331</t>
+          <t>145003; 195676</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM16_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman golosinas o caramelos varias veces al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>8,47; 26,17</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14,9; 35,89</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13,82; 27,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,27; 18,2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,93; 15,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10,44; 15,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7,67; 17,42</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,7; 16,99</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,82; 15,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,31; 16,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10,84; 15,41</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,12; 15,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1627998129983184</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2400772639193908</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1984093503814554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>8745</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11021</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19766</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.08471609657410807</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1489550428467857</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1382422976132599</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4551; 14057</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6838; 16474</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13772; 27054</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.261705023338825</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.358868765748122</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2715693089471078</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.12556985090936</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1238722889109055</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1247608442402275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>58569</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52604</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111173</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.09268744132789244</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.09930281719584777</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1044077769047811</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>43232; 84900</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>42171; 64289</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93037; 141978</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.182023221923051</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.151387051129302</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1593307372562119</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1216323440040897</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1155067346099866</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.118760298898547</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>20274</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16996</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.07668001517506869</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.07700985686444742</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.08821803331911524</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>12781; 29037</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11331; 24997</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27685; 48607</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1742018988878279</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1698826943569739</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1548845979473829</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1275259157882725</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1305152979457111</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1289414198366062</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>87588</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>80621</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168209</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1030546284068539</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1084364785281871</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.111152987513049</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>70780; 112471</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>66982; 95205</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>145003; 195676</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1637551334233364</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1541258067780977</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1499966716616777</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman golosinas o caramelos varias veces al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>8745</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11021</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>19766</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4551</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6838</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13772</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>14057</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>16474</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>27054</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>58569</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>52604</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>111173</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>43232</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>42171</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>93037</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>84900</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>64289</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>141978</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>20274</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>16996</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>37270</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>12781</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>11331</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>27685</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>29037</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>24997</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>48607</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>87588</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>80621</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>168209</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>70780</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>66982</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>145003</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>112471</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>95205</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>195676</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>